--- a/questionnaire_templates/040_sleep_consultation_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/040_sleep_consultation_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'6-7_hours'}</t>
+          <t>6-7_hours</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '6-7 hours'}</t>
+          <t>6-7 hours</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'7-8_hours'}</t>
+          <t>7-8_hours</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '7-8 hours'}</t>
+          <t>7-8 hours</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'8-9_hours'}</t>
+          <t>8-9_hours</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '8-9 hours'}</t>
+          <t>8-9 hours</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'10_hours_or_more'}</t>
+          <t>10_hours_or_more</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '10 hours or more'}</t>
+          <t>10 hours or more</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'almost_every_night'}</t>
+          <t>almost_every_night</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Almost Every Night'}</t>
+          <t>Almost Every Night</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'sleep_apnea'}</t>
+          <t>sleep_apnea</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Sleep Apnea'}</t>
+          <t>Sleep Apnea</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'insomnia'}</t>
+          <t>insomnia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Insomnia'}</t>
+          <t>Insomnia</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'narcolepsy'}</t>
+          <t>narcolepsy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Narcolepsy'}</t>
+          <t>Narcolepsy</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'lifestyle_changes'}</t>
+          <t>lifestyle_changes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Lifestyle Changes'}</t>
+          <t>Lifestyle Changes</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
